--- a/docs/learn/writing-taxonomy/Writing_Taxonomy_v1.xlsx
+++ b/docs/learn/writing-taxonomy/Writing_Taxonomy_v1.xlsx
@@ -401,7 +401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" style="20" min="1" max="1"/>
@@ -703,6 +703,18 @@
       <c r="B26" t="inlineStr">
         <is>
           <t>項目內含「/」或「／」者是否應再拆分未由 Owner 裁決，一律標為 NEEDS_OWNER_REVIEW，不自行拆分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sub-skill 歧義裁決</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-30 Owner 裁決 12 個 NEEDS_OWNER_REVIEW：H1-1「words / phrases / clauses 的平行」拆為 3 個；H4-5 五種感官意象拆為 5 個；其餘 10 個維持單一 node 並改為 ACTIVE。總數 140 → 146。</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4927,23 +4939,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARALLEL_WORDS_PHRASES_CLAUSES</t>
+          <t>WRITE_HSF_PARALLEL_WORD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>words / phrases / clauses 的平行</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>單字層級平行</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Word Parallelism</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「words / phrases / clauses 的平行」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -4985,22 +5001,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARALLEL_PAIRED_STRUCTURES</t>
+          <t>WRITE_HSF_PARALLEL_PHRASE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>成對結構</t>
+          <t>片語層級平行</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>paired structures</t>
+          <t>Phrase Parallelism</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「words / phrases / clauses 的平行」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5047,22 +5063,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARALLEL_NOT_ONLY_BUT_ALSO</t>
+          <t>WRITE_HSF_PARALLEL_CLAUSE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>not only…but also 句型</t>
+          <t>子句層級平行</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>not only…but also</t>
+          <t>Clause Parallelism</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「words / phrases / clauses 的平行」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5109,17 +5125,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARALLEL_BOTH_AND</t>
+          <t>WRITE_HSF_PARALLEL_PAIRED_STRUCTURES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>both…and 句型</t>
+          <t>成對結構</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>both…and</t>
+          <t>paired structures</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5156,30 +5172,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H1-2</t>
+          <t>H1-1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WRITE_HSF_SENT_VARIETY</t>
+          <t>WRITE_HSF_PARALLEL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>H1-2-1</t>
+          <t>H1-1-5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WRITE_HSF_SENT_VARIETY_SUB01</t>
+          <t>WRITE_HSF_PARALLEL_NOT_ONLY_BUT_ALSO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>長短句交替</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>not only…but also 句型</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>not only…but also</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -5214,32 +5234,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H1-2</t>
+          <t>H1-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WRITE_HSF_SENT_VARIETY</t>
+          <t>WRITE_HSF_PARALLEL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>H1-2-2</t>
+          <t>H1-1-6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WRITE_HSF_SENT_VARIETY_SIMPLE_COMPOUND_COMPLEX_VARIATION</t>
+          <t>WRITE_HSF_PARALLEL_BOTH_AND</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>簡單／複合／複雜句交替</t>
+          <t>both…and 句型</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>simple / compound / complex variation</t>
+          <t>both…and</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5249,7 +5269,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -5286,20 +5306,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>H1-2-3</t>
+          <t>H1-2-1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WRITE_HSF_SENT_VARIETY_SUB03</t>
+          <t>WRITE_HSF_SENT_VARIETY_SUB01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>不同句首</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>長短句交替</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -5344,23 +5363,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>H1-2-4</t>
+          <t>H1-2-2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WRITE_HSF_SENT_VARIETY_SUB04</t>
+          <t>WRITE_HSF_SENT_VARIETY_SIMPLE_COMPOUND_COMPLEX_VARIATION</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>避免單一句型反覆</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>句型交替變化</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sentence-type Variation</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「簡單／複合／複雜句交替」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5392,32 +5415,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H1-3</t>
+          <t>H1-2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COMPLEX</t>
+          <t>WRITE_HSF_SENT_VARIETY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>H1-3-1</t>
+          <t>H1-2-3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COMPLEX_RELATIVE_CLAUSES</t>
+          <t>WRITE_HSF_SENT_VARIETY_SUB03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>關係子句</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>relative clauses</t>
+          <t>不同句首</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5454,32 +5472,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H1-3</t>
+          <t>H1-2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COMPLEX</t>
+          <t>WRITE_HSF_SENT_VARIETY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>H1-3-2</t>
+          <t>H1-2-4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COMPLEX_NOUN_CLAUSES</t>
+          <t>WRITE_HSF_SENT_VARIETY_SUB04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>名詞子句</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>noun clauses</t>
+          <t>避免單一句型反覆</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5526,22 +5539,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>H1-3-3</t>
+          <t>H1-3-1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COMPLEX_ADVERB_CLAUSES</t>
+          <t>WRITE_HSF_COMPLEX_RELATIVE_CLAUSES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>副詞子句</t>
+          <t>關係子句</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>adverb clauses</t>
+          <t>relative clauses</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5588,20 +5601,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H1-3-4</t>
+          <t>H1-3-2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COMPLEX_SUB04</t>
+          <t>WRITE_HSF_COMPLEX_NOUN_CLAUSES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>多層從屬但仍清楚易讀</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>名詞子句</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>noun clauses</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -5636,32 +5653,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H1-4</t>
+          <t>H1-3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REDUCED</t>
+          <t>WRITE_HSF_COMPLEX</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1-4-1</t>
+          <t>H1-3-3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REDUCED_V_ING_PARTICIPIAL_PHRASES</t>
+          <t>WRITE_HSF_COMPLEX_ADVERB_CLAUSES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>V-ing 分詞片語</t>
+          <t>副詞子句</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>V-ing participial phrases</t>
+          <t>adverb clauses</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5698,32 +5715,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H1-4</t>
+          <t>H1-3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REDUCED</t>
+          <t>WRITE_HSF_COMPLEX</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>H1-4-2</t>
+          <t>H1-3-4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REDUCED_P_P_PHRASES</t>
+          <t>WRITE_HSF_COMPLEX_SUB04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p.p. 分詞片語</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>p.p. phrases</t>
+          <t>多層從屬但仍清楚易讀</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5770,22 +5782,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>H1-4-3</t>
+          <t>H1-4-1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REDUCED_REDUCED_RELATIVE_CLAUSES</t>
+          <t>WRITE_HSF_REDUCED_V_ING_PARTICIPIAL_PHRASES</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>簡化關係子句</t>
+          <t>V-ing 分詞片語</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reduced relative clauses</t>
+          <t>V-ing participial phrases</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5832,20 +5844,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>H1-4-4</t>
+          <t>H1-4-2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REDUCED_WITH_O_COMPLEMENT</t>
+          <t>WRITE_HSF_REDUCED_P_P_PHRASES</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>with + O + complement 等簡化</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>p.p. 分詞片語</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>p.p. phrases</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -5880,32 +5896,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H1-5</t>
+          <t>H1-4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INVERSION</t>
+          <t>WRITE_HSF_REDUCED</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>H1-5-1</t>
+          <t>H1-4-3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INVERSION_NEGATIVE_INVERSION</t>
+          <t>WRITE_HSF_REDUCED_REDUCED_RELATIVE_CLAUSES</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>否定倒裝</t>
+          <t>簡化關係子句</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>negative inversion</t>
+          <t>reduced relative clauses</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5942,32 +5958,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H1-5</t>
+          <t>H1-4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INVERSION</t>
+          <t>WRITE_HSF_REDUCED</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>H1-5-2</t>
+          <t>H1-4-4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INVERSION_ONLY_ADV_INVERSION</t>
+          <t>WRITE_HSF_REDUCED_WITH_O_COMPLEMENT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>only + 副詞倒裝</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>only + adv inversion</t>
+          <t>with + O + complement 等簡化</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6014,22 +6025,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>H1-5-3</t>
+          <t>H1-5-1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INVERSION_SO_SUCH_INVERSION</t>
+          <t>WRITE_HSF_INVERSION_NEGATIVE_INVERSION</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>so／such 倒裝</t>
+          <t>否定倒裝</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>so/such inversion</t>
+          <t>negative inversion</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6039,7 +6050,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6076,22 +6087,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>H1-5-4</t>
+          <t>H1-5-2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INVERSION_CONDITIONAL_INVERSION</t>
+          <t>WRITE_HSF_INVERSION_ONLY_ADV_INVERSION</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>條件句倒裝</t>
+          <t>only + 副詞倒裝</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>conditional inversion</t>
+          <t>only + adv inversion</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6128,37 +6139,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H1-6</t>
+          <t>H1-5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE</t>
+          <t>WRITE_HSF_INVERSION</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>H1-6-1</t>
+          <t>H1-5-3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE_APPOSITIVES</t>
+          <t>WRITE_HSF_INVERSION_SO_SUCH_INVERSION</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>同位語</t>
+          <t>so／such 倒裝</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>appositives</t>
+          <t>So/Such Inversion</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「so／such 倒裝」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -6190,30 +6201,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H1-6</t>
+          <t>H1-5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE</t>
+          <t>WRITE_HSF_INVERSION</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>H1-6-2</t>
+          <t>H1-5-4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE_SUB02</t>
+          <t>WRITE_HSF_INVERSION_CONDITIONAL_INVERSION</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>插入補充</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>條件句倒裝</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>conditional inversion</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -6258,22 +6273,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>H1-6-3</t>
+          <t>H1-6-1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE_DASH_STRUCTURES</t>
+          <t>WRITE_HSF_APPOSITIVE_APPOSITIVES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>破折號結構</t>
+          <t>同位語</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>dash structures</t>
+          <t>appositives</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6320,22 +6335,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>H1-6-4</t>
+          <t>H1-6-2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE_COLON_EXPANSION</t>
+          <t>WRITE_HSF_APPOSITIVE_SUB02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>冒號展開</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>colon expansion</t>
+          <t>插入補充</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6382,22 +6392,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>H1-6-5</t>
+          <t>H1-6-3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WRITE_HSF_APPOSITIVE_NON_RESTRICTIVE_SUPPLEMENTARY_PHRASES</t>
+          <t>WRITE_HSF_APPOSITIVE_DASH_STRUCTURES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>非限定補充片語</t>
+          <t>破折號結構</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>non-restrictive supplementary phrases</t>
+          <t>dash structures</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6429,35 +6439,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2-1</t>
+          <t>H1-6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_VARIETY</t>
+          <t>WRITE_HSF_APPOSITIVE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>H2-1-1</t>
+          <t>H1-6-4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_VARIETY_SUB01</t>
+          <t>WRITE_HSF_APPOSITIVE_COLON_EXPANSION</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>避免不必要重複</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>冒號展開</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>colon expansion</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -6487,35 +6501,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2-1</t>
+          <t>H1-6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_VARIETY</t>
+          <t>WRITE_HSF_APPOSITIVE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>H2-1-2</t>
+          <t>H1-6-5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_VARIETY_SUB02</t>
+          <t>WRITE_HSF_APPOSITIVE_NON_RESTRICTIVE_SUPPLEMENTARY_PHRASES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>不同詞彙表達相關概念</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>非限定補充片語</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>non-restrictive supplementary phrases</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -6560,20 +6578,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>H2-1-3</t>
+          <t>H2-1-1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_VARIETY_SUB03</t>
+          <t>WRITE_HSF_LEX_VARIETY_SUB01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>動詞／形容詞／名詞變化</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>避免不必要重複</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -6581,7 +6598,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -6608,32 +6625,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2-2</t>
+          <t>H2-1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_PRECISION</t>
+          <t>WRITE_HSF_LEX_VARIETY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>H2-2-1</t>
+          <t>H2-1-2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_PRECISION_SPECIFIC_VERBS</t>
+          <t>WRITE_HSF_LEX_VARIETY_SUB02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>精準動詞</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>specific verbs</t>
+          <t>不同詞彙表達相關概念</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6670,37 +6682,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2-2</t>
+          <t>H2-1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_PRECISION</t>
+          <t>WRITE_HSF_LEX_VARIETY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>H2-2-2</t>
+          <t>H2-1-3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_PRECISION_PRECISE_NOUNS</t>
+          <t>WRITE_HSF_LEX_VARIETY_SUB03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>精準名詞</t>
+          <t>詞類／詞彙變化</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>precise nouns</t>
+          <t>Word-class / Lexical Variation</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「動詞／形容詞／名詞變化」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -6742,20 +6754,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>H2-2-3</t>
+          <t>H2-2-1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_PRECISION_ADJECTIVE_ADVERB</t>
+          <t>WRITE_HSF_LEX_PRECISION_SPECIFIC_VERBS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>適切 adjective/adverb</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>精準動詞</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>specific verbs</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -6763,7 +6779,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -6800,20 +6816,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>H2-2-4</t>
+          <t>H2-2-2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_PRECISION_SUB04</t>
+          <t>WRITE_HSF_LEX_PRECISION_PRECISE_NOUNS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>細微語義差異</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>精準名詞</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>precise nouns</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -6848,37 +6868,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2-3</t>
+          <t>H2-2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ADV_VOCAB</t>
+          <t>WRITE_HSF_LEX_PRECISION</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>H2-3-1</t>
+          <t>H2-2-3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ADV_VOCAB_SOPHISTICATED_BUT_NATURAL_VOCABULARY</t>
+          <t>WRITE_HSF_LEX_PRECISION_ADJECTIVE_ADVERB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>成熟且自然的詞彙</t>
+          <t>適切修飾語選擇</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>sophisticated but natural vocabulary</t>
+          <t>Appropriate Modifier Choice</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「適切 adjective/adverb」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -6910,32 +6930,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2-3</t>
+          <t>H2-2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ADV_VOCAB</t>
+          <t>WRITE_HSF_LEX_PRECISION</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>H2-3-2</t>
+          <t>H2-2-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ADV_VOCAB_ACADEMIC_VOCABULARY</t>
+          <t>WRITE_HSF_LEX_PRECISION_SUB04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>學術詞彙</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>academic vocabulary</t>
+          <t>細微語義差異</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6982,20 +6997,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>H2-3-3</t>
+          <t>H2-3-1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ADV_VOCAB_SUB03</t>
+          <t>WRITE_HSF_ADV_VOCAB_SOPHISTICATED_BUT_NATURAL_VOCABULARY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>避免硬塞難字</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>成熟且自然的詞彙</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>sophisticated but natural vocabulary</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -7030,32 +7049,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2-4</t>
+          <t>H2-3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION</t>
+          <t>WRITE_HSF_ADV_VOCAB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>H2-4-1</t>
+          <t>H2-3-2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION_VERB_NOUN</t>
+          <t>WRITE_HSF_ADV_VOCAB_ACADEMIC_VOCABULARY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>動詞－名詞搭配</t>
+          <t>學術詞彙</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>verb–noun</t>
+          <t>academic vocabulary</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7092,32 +7111,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2-4</t>
+          <t>H2-3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION</t>
+          <t>WRITE_HSF_ADV_VOCAB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>H2-4-2</t>
+          <t>H2-3-3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION_ADJECTIVE_NOUN</t>
+          <t>WRITE_HSF_ADV_VOCAB_SUB03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>形容詞－名詞搭配</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>adjective–noun</t>
+          <t>避免硬塞難字</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7164,22 +7178,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>H2-4-3</t>
+          <t>H2-4-1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION_ADVERB_ADJECTIVE</t>
+          <t>WRITE_HSF_COLLOCATION_VERB_NOUN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>副詞－形容詞搭配</t>
+          <t>動詞－名詞搭配</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>adverb–adjective</t>
+          <t>verb–noun</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7226,22 +7240,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>H2-4-4</t>
+          <t>H2-4-2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION_PREPOSITIONAL_COLLOCATIONS</t>
+          <t>WRITE_HSF_COLLOCATION_ADJECTIVE_NOUN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>介係詞搭配</t>
+          <t>形容詞－名詞搭配</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>prepositional collocations</t>
+          <t>adjective–noun</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7288,20 +7302,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>H2-4-5</t>
+          <t>H2-4-3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WRITE_HSF_COLLOCATION_SUB05</t>
+          <t>WRITE_HSF_COLLOCATION_ADVERB_ADJECTIVE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>慣用搭配</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>副詞－形容詞搭配</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>adverb–adjective</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -7336,32 +7354,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H2-5</t>
+          <t>H2-4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE</t>
+          <t>WRITE_HSF_COLLOCATION</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>H2-5-1</t>
+          <t>H2-4-4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE_SYNONYMS</t>
+          <t>WRITE_HSF_COLLOCATION_PREPOSITIONAL_COLLOCATIONS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>同義詞</t>
+          <t>介係詞搭配</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>synonyms</t>
+          <t>prepositional collocations</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7398,32 +7416,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H2-5</t>
+          <t>H2-4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE</t>
+          <t>WRITE_HSF_COLLOCATION</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>H2-5-2</t>
+          <t>H2-4-5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE_NEAR_SYNONYMS</t>
+          <t>WRITE_HSF_COLLOCATION_SUB05</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>近義詞</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>near-synonyms</t>
+          <t>慣用搭配</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7470,22 +7483,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>H2-5-3</t>
+          <t>H2-5-1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE_PHRASE_REPLACEMENT</t>
+          <t>WRITE_HSF_PARAPHRASE_SYNONYMS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>片語替換</t>
+          <t>同義詞</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>phrase replacement</t>
+          <t>synonyms</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7532,22 +7545,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>H2-5-4</t>
+          <t>H2-5-2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE_CONCEPTUAL_REWORDING</t>
+          <t>WRITE_HSF_PARAPHRASE_NEAR_SYNONYMS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>概念改寫</t>
+          <t>近義詞</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>conceptual rewording</t>
+          <t>near-synonyms</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7594,20 +7607,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>H2-5-5</t>
+          <t>H2-5-3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARAPHRASE_SUB05</t>
+          <t>WRITE_HSF_PARAPHRASE_PHRASE_REPLACEMENT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>避免原詞重複</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>片語替換</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>phrase replacement</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -7637,37 +7654,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H3-1</t>
+          <t>H2-5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS</t>
+          <t>WRITE_HSF_PARAPHRASE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>H3-1-1</t>
+          <t>H2-5-4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_ADDITION</t>
+          <t>WRITE_HSF_PARAPHRASE_CONCEPTUAL_REWORDING</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>增補轉承</t>
+          <t>概念改寫</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>addition</t>
+          <t>conceptual rewording</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7699,37 +7716,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H3-1</t>
+          <t>H2-5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS</t>
+          <t>WRITE_HSF_PARAPHRASE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>H3-1-2</t>
+          <t>H2-5-5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_CONTRAST</t>
+          <t>WRITE_HSF_PARAPHRASE_SUB05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>對比轉承</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>contrast</t>
+          <t>避免原詞重複</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7776,22 +7788,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>H3-1-3</t>
+          <t>H3-1-1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_CAUSE_EFFECT</t>
+          <t>WRITE_HSF_TRANSITIONS_ADDITION</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>因果轉承</t>
+          <t>增補轉承</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>cause-effect</t>
+          <t>addition</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7838,22 +7850,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>H3-1-4</t>
+          <t>H3-1-2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_EXAMPLE</t>
+          <t>WRITE_HSF_TRANSITIONS_CONTRAST</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>舉例轉承</t>
+          <t>對比轉承</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>contrast</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7900,22 +7912,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>H3-1-5</t>
+          <t>H3-1-3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_CONCESSION</t>
+          <t>WRITE_HSF_TRANSITIONS_CAUSE_EFFECT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>讓步轉承</t>
+          <t>因果轉承</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>concession</t>
+          <t>cause-effect</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7962,22 +7974,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>H3-1-6</t>
+          <t>H3-1-4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_SEQUENCE</t>
+          <t>WRITE_HSF_TRANSITIONS_EXAMPLE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>順序轉承</t>
+          <t>舉例轉承</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>sequence</t>
+          <t>example</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8024,22 +8036,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>H3-1-7</t>
+          <t>H3-1-5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_SUMMARY_TRANSITIONS</t>
+          <t>WRITE_HSF_TRANSITIONS_CONCESSION</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>總結轉承</t>
+          <t>讓步轉承</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>summary transitions</t>
+          <t>concession</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8086,20 +8098,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>H3-1-8</t>
+          <t>H3-1-6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>WRITE_HSF_TRANSITIONS_SUB08</t>
+          <t>WRITE_HSF_TRANSITIONS_SEQUENCE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>隱性轉承</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>順序轉承</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -8134,32 +8150,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H3-2</t>
+          <t>H3-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION</t>
+          <t>WRITE_HSF_TRANSITIONS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>H3-2-1</t>
+          <t>H3-1-7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION_REPETITION_OF_KEY_CONCEPTS</t>
+          <t>WRITE_HSF_TRANSITIONS_SUMMARY_TRANSITIONS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>關鍵概念重述</t>
+          <t>總結轉承</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>repetition of key concepts</t>
+          <t>summary transitions</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8196,32 +8212,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H3-2</t>
+          <t>H3-1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION</t>
+          <t>WRITE_HSF_TRANSITIONS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>H3-2-2</t>
+          <t>H3-1-8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION_SYNONYM_CHAIN</t>
+          <t>WRITE_HSF_TRANSITIONS_SUB08</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>同義詞鏈</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>synonym chain</t>
+          <t>隱性轉承</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8268,22 +8279,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>H3-2-3</t>
+          <t>H3-2-1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION_SEMANTIC_FIELD</t>
+          <t>WRITE_HSF_LEX_COHESION_REPETITION_OF_KEY_CONCEPTS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>語意場</t>
+          <t>關鍵概念重述</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>semantic field</t>
+          <t>repetition of key concepts</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8330,22 +8341,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>H3-2-4</t>
+          <t>H3-2-2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION_SUPERORDINATE_SUBORDINATE_TERMS</t>
+          <t>WRITE_HSF_LEX_COHESION_SYNONYM_CHAIN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>上位／下位詞</t>
+          <t>同義詞鏈</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>superordinate/subordinate terms</t>
+          <t>synonym chain</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8355,7 +8366,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8392,22 +8403,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>H3-2-5</t>
+          <t>H3-2-3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LEX_COHESION_LEXICAL_RECURRENCE</t>
+          <t>WRITE_HSF_LEX_COHESION_SEMANTIC_FIELD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>詞彙復現</t>
+          <t>語意場</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>lexical recurrence</t>
+          <t>semantic field</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8444,42 +8455,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H3-3</t>
+          <t>H3-2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION</t>
+          <t>WRITE_HSF_LEX_COHESION</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>H3-3-1</t>
+          <t>H3-2-4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION_THIS_THAT_THESE_THOSE</t>
+          <t>WRITE_HSF_LEX_COHESION_SUPERORDINATE_SUBORDINATE_TERMS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>this／that／these／those 指涉</t>
+          <t>上位／下位詞關係</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>this/that/these/those</t>
+          <t>Superordinate / Subordinate Lexical Relation</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「上位／下位詞」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8506,32 +8517,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H3-3</t>
+          <t>H3-2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION</t>
+          <t>WRITE_HSF_LEX_COHESION</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>H3-3-2</t>
+          <t>H3-2-5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION_IT_THEY</t>
+          <t>WRITE_HSF_LEX_COHESION_LEXICAL_RECURRENCE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>it／they 指涉</t>
+          <t>詞彙復現</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>it/they</t>
+          <t>lexical recurrence</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8541,7 +8552,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8578,27 +8589,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>H3-3-3</t>
+          <t>H3-3-1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION_SUCH_N</t>
+          <t>WRITE_HSF_REF_COHESION_THIS_THAT_THESE_THOSE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>such + N 指涉</t>
+          <t>指示詞指涉</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>such + N</t>
+          <t>Demonstrative Reference</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「this／that／these／those 指涉」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8640,32 +8651,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>H3-3-4</t>
+          <t>H3-3-2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION_THE_FORMER_LATTER</t>
+          <t>WRITE_HSF_REF_COHESION_IT_THEY</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>the former／latter 指涉</t>
+          <t>代名詞指涉</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>the former/latter</t>
+          <t>Pronoun Reference</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「it／they 指涉」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8702,22 +8713,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>H3-3-5</t>
+          <t>H3-3-3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>WRITE_HSF_REF_COHESION_CLEAR_BACKWARD_REFERENCE</t>
+          <t>WRITE_HSF_REF_COHESION_SUCH_N</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>清楚的回指</t>
+          <t>such + N 指涉</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>clear backward reference</t>
+          <t>such + N</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8754,37 +8765,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H3-4</t>
+          <t>H3-3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INFO_FLOW</t>
+          <t>WRITE_HSF_REF_COHESION</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>H3-4-1</t>
+          <t>H3-3-4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INFO_FLOW_GIVEN_NEW_INFORMATION</t>
+          <t>WRITE_HSF_REF_COHESION_THE_FORMER_LATTER</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>已知→新資訊</t>
+          <t>the former／latter 指涉</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>given → new information</t>
+          <t>Former/Latter Reference</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「the former／latter 指涉」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8816,32 +8827,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H3-4</t>
+          <t>H3-3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INFO_FLOW</t>
+          <t>WRITE_HSF_REF_COHESION</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>H3-4-2</t>
+          <t>H3-3-5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INFO_FLOW_SENTENCE_TO_SENTENCE_PROGRESSION</t>
+          <t>WRITE_HSF_REF_COHESION_CLEAR_BACKWARD_REFERENCE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>句與句遞進</t>
+          <t>清楚的回指</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>sentence-to-sentence progression</t>
+          <t>clear backward reference</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8888,22 +8899,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>H3-4-3</t>
+          <t>H3-4-1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INFO_FLOW_A_B_C_DEVELOPMENT</t>
+          <t>WRITE_HSF_INFO_FLOW_GIVEN_NEW_INFORMATION</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>A→B→C 推展</t>
+          <t>已知→新資訊</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A→B→C development</t>
+          <t>given → new information</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8950,20 +8961,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>H3-4-4</t>
+          <t>H3-4-2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INFO_FLOW_ABRUPT_TOPIC_JUMPS</t>
+          <t>WRITE_HSF_INFO_FLOW_SENTENCE_TO_SENTENCE_PROGRESSION</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>避免 abrupt topic jumps</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>句與句遞進</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>sentence-to-sentence progression</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -8998,30 +9013,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>H3-5</t>
+          <t>H3-4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARA_PROGRESSION</t>
+          <t>WRITE_HSF_INFO_FLOW</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>H3-5-1</t>
+          <t>H3-4-3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARA_PROGRESSION_SUB01</t>
+          <t>WRITE_HSF_INFO_FLOW_A_B_C_DEVELOPMENT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>前段→後段邏輯承接</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>A→B→C 推展</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>A→B→C development</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -9056,32 +9075,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>H3-5</t>
+          <t>H3-4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARA_PROGRESSION</t>
+          <t>WRITE_HSF_INFO_FLOW</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>H3-5-2</t>
+          <t>H3-4-4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARA_PROGRESSION_BRIDGE_SENTENCE</t>
+          <t>WRITE_HSF_INFO_FLOW_ABRUPT_TOPIC_JUMPS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>橋接句</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>bridge sentence</t>
+          <t>避免 abrupt topic jumps</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9128,22 +9142,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>H3-5-3</t>
+          <t>H3-5-1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARA_PROGRESSION_CONCEPT_CARRY_OVER</t>
+          <t>WRITE_HSF_PARA_PROGRESSION_SUB01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>概念承接</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>concept carry-over</t>
+          <t>前段→後段邏輯承接</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9190,20 +9199,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>H3-5-4</t>
+          <t>H3-5-2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PARA_PROGRESSION_SUB04</t>
+          <t>WRITE_HSF_PARA_PROGRESSION_BRIDGE_SENTENCE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>段落功能順序</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>橋接句</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>bridge sentence</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -9238,32 +9251,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H3-6</t>
+          <t>H3-5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK</t>
+          <t>WRITE_HSF_PARA_PROGRESSION</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>H3-6-1</t>
+          <t>H3-5-3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK_INTRODUCTION_CONCLUSION_ECHO</t>
+          <t>WRITE_HSF_PARA_PROGRESSION_CONCEPT_CARRY_OVER</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>首尾呼應</t>
+          <t>概念承接</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>introduction–conclusion echo</t>
+          <t>concept carry-over</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9300,32 +9313,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>H3-6</t>
+          <t>H3-5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK</t>
+          <t>WRITE_HSF_PARA_PROGRESSION</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>H3-6-2</t>
+          <t>H3-5-4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK_MOTIF_CALLBACK</t>
+          <t>WRITE_HSF_PARA_PROGRESSION_SUB04</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>母題回扣</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>motif callback</t>
+          <t>段落功能順序</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9372,22 +9380,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>H3-6-3</t>
+          <t>H3-6-1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK_KEY_PHRASE_RETURN</t>
+          <t>WRITE_HSF_CALLBACK_INTRODUCTION_CONCLUSION_ECHO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>關鍵語句重現</t>
+          <t>首尾呼應</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>key phrase return</t>
+          <t>introduction–conclusion echo</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9434,22 +9442,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>H3-6-4</t>
+          <t>H3-6-2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK_OPENING_IMAGE_REVISITED</t>
+          <t>WRITE_HSF_CALLBACK_MOTIF_CALLBACK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>開場意象重訪</t>
+          <t>母題回扣</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>opening image revisited</t>
+          <t>motif callback</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9496,22 +9504,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>H3-6-5</t>
+          <t>H3-6-3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CALLBACK_CENTRAL_IDEA_RECURRENCE</t>
+          <t>WRITE_HSF_CALLBACK_KEY_PHRASE_RETURN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>核心概念復現</t>
+          <t>關鍵語句重現</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>central idea recurrence</t>
+          <t>key phrase return</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9543,37 +9551,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>H4-1</t>
+          <t>H3-6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST</t>
+          <t>WRITE_HSF_CALLBACK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>H4-1-1</t>
+          <t>H3-6-4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST_CONTRAST</t>
+          <t>WRITE_HSF_CALLBACK_OPENING_IMAGE_REVISITED</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>對比轉承</t>
+          <t>開場意象重訪</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>contrast</t>
+          <t>opening image revisited</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9605,37 +9613,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>H4-1</t>
+          <t>H3-6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST</t>
+          <t>WRITE_HSF_CALLBACK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>H4-1-2</t>
+          <t>H3-6-5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST_ANTITHESIS</t>
+          <t>WRITE_HSF_CALLBACK_CENTRAL_IDEA_RECURRENCE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>對偶反襯</t>
+          <t>核心概念復現</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>antithesis</t>
+          <t>central idea recurrence</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9682,22 +9690,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>H4-1-3</t>
+          <t>H4-1-1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST_JUXTAPOSITION</t>
+          <t>WRITE_HSF_CONTRAST_CONTRAST</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>並置</t>
+          <t>對比轉承</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>juxtaposition</t>
+          <t>contrast</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9744,22 +9752,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>H4-1-4</t>
+          <t>H4-1-2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST_BEFORE_AFTER</t>
+          <t>WRITE_HSF_CONTRAST_ANTITHESIS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>前後對照</t>
+          <t>對偶反襯</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>before/after</t>
+          <t>antithesis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9769,7 +9777,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9806,22 +9814,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>H4-1-5</t>
+          <t>H4-1-3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CONTRAST_LIGHT_DARK_CONTRAST</t>
+          <t>WRITE_HSF_CONTRAST_JUXTAPOSITION</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>明暗對照</t>
+          <t>並置</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>light/dark contrast</t>
+          <t>juxtaposition</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9831,7 +9839,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9858,37 +9866,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>H4-2</t>
+          <t>H4-1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING</t>
+          <t>WRITE_HSF_CONTRAST</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>H4-2-1</t>
+          <t>H4-1-4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING_RHETORICAL_PARALLELISM</t>
+          <t>WRITE_HSF_CONTRAST_BEFORE_AFTER</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>修辭平行</t>
+          <t>前後對照</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>rhetorical parallelism</t>
+          <t>Before/After Contrast</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「前後對照」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9920,37 +9928,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>H4-2</t>
+          <t>H4-1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING</t>
+          <t>WRITE_HSF_CONTRAST</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>H4-2-2</t>
+          <t>H4-1-5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING_RULE_OF_THREE</t>
+          <t>WRITE_HSF_CONTRAST_LIGHT_DARK_CONTRAST</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>三段式</t>
+          <t>明暗對照</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rule of Three</t>
+          <t>Light/Dark Contrast</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 原文「明暗對照」。Owner 於 2026-08-30 裁決維持單一 node，不再拆分。</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9992,20 +10000,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>H4-2-3</t>
+          <t>H4-2-1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING_ANAPHORA</t>
+          <t>WRITE_HSF_PATTERNING_RHETORICAL_PARALLELISM</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>anaphora 首語重複</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>修辭平行</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>rhetorical parallelism</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -10050,22 +10062,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>H4-2-4</t>
+          <t>H4-2-2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING_REPETITION</t>
+          <t>WRITE_HSF_PATTERNING_RULE_OF_THREE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>重複</t>
+          <t>三段式</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>repetition</t>
+          <t>Rule of Three</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -10112,22 +10124,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>H4-2-5</t>
+          <t>H4-2-3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>WRITE_HSF_PATTERNING_CLIMACTIC_SEQUENCE</t>
+          <t>WRITE_HSF_PATTERNING_ANAPHORA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>漸強序列</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>climactic sequence</t>
+          <t>anaphora 首語重複</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10164,32 +10171,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>H4-3</t>
+          <t>H4-2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WRITE_HSF_RHET_QUESTION</t>
+          <t>WRITE_HSF_PATTERNING</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>H4-3-1</t>
+          <t>H4-2-4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>WRITE_HSF_RHET_QUESTION_QUESTION_OPENING</t>
+          <t>WRITE_HSF_PATTERNING_REPETITION</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>提問開場</t>
+          <t>重複</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>question opening</t>
+          <t>repetition</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10226,32 +10233,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>H4-3</t>
+          <t>H4-2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WRITE_HSF_RHET_QUESTION</t>
+          <t>WRITE_HSF_PATTERNING</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>H4-3-2</t>
+          <t>H4-2-5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>WRITE_HSF_RHET_QUESTION_CHALLENGE_QUESTION</t>
+          <t>WRITE_HSF_PATTERNING_CLIMACTIC_SEQUENCE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>挑戰式提問</t>
+          <t>漸強序列</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>challenge question</t>
+          <t>climactic sequence</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10298,22 +10305,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>H4-3-3</t>
+          <t>H4-3-1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>WRITE_HSF_RHET_QUESTION_REFLECTIVE_QUESTION</t>
+          <t>WRITE_HSF_RHET_QUESTION_QUESTION_OPENING</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>反思式提問</t>
+          <t>提問開場</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>reflective question</t>
+          <t>question opening</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10360,22 +10367,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>H4-3-4</t>
+          <t>H4-3-2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>WRITE_HSF_RHET_QUESTION_QUESTION_ANSWER_PATTERN</t>
+          <t>WRITE_HSF_RHET_QUESTION_CHALLENGE_QUESTION</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>自問自答</t>
+          <t>挑戰式提問</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>question-answer pattern</t>
+          <t>challenge question</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10412,32 +10419,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>H4-4</t>
+          <t>H4-3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE</t>
+          <t>WRITE_HSF_RHET_QUESTION</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>H4-4-1</t>
+          <t>H4-3-3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE_SIMILE</t>
+          <t>WRITE_HSF_RHET_QUESTION_REFLECTIVE_QUESTION</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>明喻</t>
+          <t>反思式提問</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>simile</t>
+          <t>reflective question</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10474,32 +10481,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>H4-4</t>
+          <t>H4-3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE</t>
+          <t>WRITE_HSF_RHET_QUESTION</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>H4-4-2</t>
+          <t>H4-3-4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE_METAPHOR</t>
+          <t>WRITE_HSF_RHET_QUESTION_QUESTION_ANSWER_PATTERN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>隱喻</t>
+          <t>自問自答</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>metaphor</t>
+          <t>question-answer pattern</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10546,22 +10553,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>H4-4-3</t>
+          <t>H4-4-1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE_ANALOGY</t>
+          <t>WRITE_HSF_FIGURATIVE_SIMILE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>類比</t>
+          <t>明喻</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>analogy</t>
+          <t>simile</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10608,22 +10615,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>H4-4-4</t>
+          <t>H4-4-2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE_EXTENDED_METAPHOR</t>
+          <t>WRITE_HSF_FIGURATIVE_METAPHOR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>延伸隱喻</t>
+          <t>隱喻</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>extended metaphor</t>
+          <t>metaphor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10670,22 +10677,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>H4-4-5</t>
+          <t>H4-4-3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>WRITE_HSF_FIGURATIVE_PERSONIFICATION</t>
+          <t>WRITE_HSF_FIGURATIVE_ANALOGY</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>擬人</t>
+          <t>類比</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>personification</t>
+          <t>analogy</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10722,32 +10729,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>H4-5</t>
+          <t>H4-4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WRITE_HSF_IMAGERY</t>
+          <t>WRITE_HSF_FIGURATIVE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>H4-5-1</t>
+          <t>H4-4-4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>WRITE_HSF_IMAGERY_VISUAL_AUDITORY_TACTILE_OLFACTORY_GUSTATORY_IMAGERY</t>
+          <t>WRITE_HSF_FIGURATIVE_EXTENDED_METAPHOR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>visual / auditory / tactile / olfactory / gustatory imagery</t>
+          <t>延伸隱喻</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>visual / auditory / tactile / olfactory / gustatory imagery</t>
+          <t>extended metaphor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10757,7 +10764,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>NEEDS_OWNER_REVIEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10784,32 +10791,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>H4-5</t>
+          <t>H4-4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WRITE_HSF_IMAGERY</t>
+          <t>WRITE_HSF_FIGURATIVE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>H4-5-2</t>
+          <t>H4-4-5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>WRITE_HSF_IMAGERY_SENSORY_DETAILS</t>
+          <t>WRITE_HSF_FIGURATIVE_PERSONIFICATION</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>感官細節</t>
+          <t>擬人</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>sensory details</t>
+          <t>personification</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10856,27 +10863,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>H4-5-3</t>
+          <t>H4-5-1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>WRITE_HSF_IMAGERY_CONCRETE_IMAGERY</t>
+          <t>WRITE_HSF_IMAGERY_VISUAL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>具體意象</t>
+          <t>視覺意象</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>concrete imagery</t>
+          <t>Visual Imagery</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「visual / auditory / tactile / olfactory / gustatory imagery」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10908,37 +10915,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>H4-6</t>
+          <t>H4-5</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE</t>
+          <t>WRITE_HSF_IMAGERY</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>H4-6-1</t>
+          <t>H4-5-2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE_PUNCH_LINE</t>
+          <t>WRITE_HSF_IMAGERY_AUDITORY</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>收束金句</t>
+          <t>聽覺意象</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>punch line</t>
+          <t>Auditory Imagery</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「visual / auditory / tactile / olfactory / gustatory imagery」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10970,37 +10977,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>H4-6</t>
+          <t>H4-5</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE</t>
+          <t>WRITE_HSF_IMAGERY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>H4-6-2</t>
+          <t>H4-5-3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE_APHORISTIC_ENDING</t>
+          <t>WRITE_HSF_IMAGERY_TACTILE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>格言式結尾</t>
+          <t>觸覺意象</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>aphoristic ending</t>
+          <t>Tactile Imagery</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「visual / auditory / tactile / olfactory / gustatory imagery」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -11032,37 +11039,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>H4-6</t>
+          <t>H4-5</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE</t>
+          <t>WRITE_HSF_IMAGERY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>H4-6-3</t>
+          <t>H4-5-4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE_CALLBACK_ENDING</t>
+          <t>WRITE_HSF_IMAGERY_OLFACTORY</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>回扣式結尾</t>
+          <t>嗅覺意象</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>callback ending</t>
+          <t>Olfactory Imagery</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「visual / auditory / tactile / olfactory / gustatory imagery」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11094,37 +11101,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>H4-6</t>
+          <t>H4-5</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE</t>
+          <t>WRITE_HSF_IMAGERY</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>H4-6-4</t>
+          <t>H4-5-5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE_CONTRAST_ENDING</t>
+          <t>WRITE_HSF_IMAGERY_GUSTATORY</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>對比式結尾</t>
+          <t>味覺意象</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>contrast ending</t>
+          <t>Gustatory Imagery</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。 Owner 於 2026-08-30 裁決自「visual / auditory / tactile / olfactory / gustatory imagery」拆分為獨立 Sub-skill。</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11156,32 +11163,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>H4-6</t>
+          <t>H4-5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE</t>
+          <t>WRITE_HSF_IMAGERY</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>H4-6-5</t>
+          <t>H4-5-6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE_RHETORICAL_QUESTION_ENDING</t>
+          <t>WRITE_HSF_IMAGERY_SENSORY_DETAILS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>提問式結尾</t>
+          <t>感官細節</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>rhetorical question ending</t>
+          <t>sensory details</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11218,32 +11225,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>H4-6</t>
+          <t>H4-5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE</t>
+          <t>WRITE_HSF_IMAGERY</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>H4-6-6</t>
+          <t>H4-5-7</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>WRITE_HSF_POWERFUL_CLOSE_MEMORABLE_FINAL_SENTENCE</t>
+          <t>WRITE_HSF_IMAGERY_CONCRETE_IMAGERY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>令人印象深刻的結尾句</t>
+          <t>具體意象</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>memorable final sentence</t>
+          <t>concrete imagery</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11275,37 +11282,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>H5-1</t>
+          <t>H4-6</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>H5-1-1</t>
+          <t>H4-6-1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS_CENTRAL_IDEA</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE_PUNCH_LINE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>核心概念</t>
+          <t>收束金句</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>central idea</t>
+          <t>punch line</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11337,37 +11344,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>H5-1</t>
+          <t>H4-6</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>H5-1-2</t>
+          <t>H4-6-2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS_CONTROLLING_IDEA</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE_APHORISTIC_ENDING</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>統攝概念</t>
+          <t>格言式結尾</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>controlling idea</t>
+          <t>aphoristic ending</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11399,35 +11406,39 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>H5-1</t>
+          <t>H4-6</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>H5-1-3</t>
+          <t>H4-6-3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS_THESIS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE_CALLBACK_ENDING</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>thesis（論說文）</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
+          <t>回扣式結尾</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>callback ending</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -11457,37 +11468,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>H5-1</t>
+          <t>H4-6</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>H5-1-4</t>
+          <t>H4-6-4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS_PARAGRAPH_FOCUS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE_CONTRAST_ENDING</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>段落焦點</t>
+          <t>對比式結尾</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>paragraph focus</t>
+          <t>contrast ending</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11519,37 +11530,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>H5-1</t>
+          <t>H4-6</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>H5-1-5</t>
+          <t>H4-6-5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>WRITE_HSF_CLEAR_FOCUS_PURPOSE_AWARENESS</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE_RHETORICAL_QUESTION_ENDING</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>寫作目的意識</t>
+          <t>提問式結尾</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>purpose awareness</t>
+          <t>rhetorical question ending</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11581,37 +11592,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>H5-2</t>
+          <t>H4-6</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>H5-2-1</t>
+          <t>H4-6-6</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_SPECIFICITY</t>
+          <t>WRITE_HSF_POWERFUL_CLOSE_MEMORABLE_FINAL_SENTENCE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>具體性</t>
+          <t>令人印象深刻的結尾句</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>specificity</t>
+          <t>memorable final sentence</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11648,32 +11659,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>H5-2</t>
+          <t>H5-1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>H5-2-2</t>
+          <t>H5-1-1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_CONCRETIZATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS_CENTRAL_IDEA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>具象化</t>
+          <t>核心概念</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>concretization</t>
+          <t>central idea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11710,32 +11721,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>H5-2</t>
+          <t>H5-1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>H5-2-3</t>
+          <t>H5-1-2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_EFFECTIVE_EXAMPLES</t>
+          <t>WRITE_HSF_CLEAR_FOCUS_CONTROLLING_IDEA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>有效例證</t>
+          <t>統攝概念</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>effective examples</t>
+          <t>controlling idea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11772,32 +11783,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>H5-2</t>
+          <t>H5-1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>H5-2-4</t>
+          <t>H5-1-3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_ILLUSTRATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS_THESIS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>例示</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>illustration</t>
+          <t>thesis（論說文）</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -11834,32 +11840,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>H5-2</t>
+          <t>H5-1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>H5-2-5</t>
+          <t>H5-1-4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_EXPLANATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS_PARAGRAPH_FOCUS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>解釋</t>
+          <t>段落焦點</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>explanation</t>
+          <t>paragraph focus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11896,32 +11902,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>H5-2</t>
+          <t>H5-1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION</t>
+          <t>WRITE_HSF_CLEAR_FOCUS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>H5-2-6</t>
+          <t>H5-1-5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_DETAIL</t>
+          <t>WRITE_HSF_CLEAR_FOCUS_PURPOSE_AWARENESS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>細節</t>
+          <t>寫作目的意識</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>purpose awareness</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11968,22 +11974,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>H5-2-7</t>
+          <t>H5-2-1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>WRITE_HSF_ELABORATION_IDEA_EXPLAIN_EXTEND</t>
+          <t>WRITE_HSF_ELABORATION_SPECIFICITY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Idea → Explain → Extend 展開</t>
+          <t>具體性</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Idea → Explain → Extend</t>
+          <t>specificity</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12020,32 +12026,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>H5-3</t>
+          <t>H5-2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC</t>
+          <t>WRITE_HSF_ELABORATION</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>H5-3-1</t>
+          <t>H5-2-2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC_CAUSE_EFFECT</t>
+          <t>WRITE_HSF_ELABORATION_CONCRETIZATION</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>因果轉承</t>
+          <t>具象化</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>cause-effect</t>
+          <t>concretization</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12082,32 +12088,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>H5-3</t>
+          <t>H5-2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC</t>
+          <t>WRITE_HSF_ELABORATION</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>H5-3-2</t>
+          <t>H5-2-3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC_CAUSAL_CHAIN</t>
+          <t>WRITE_HSF_ELABORATION_EFFECTIVE_EXAMPLES</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>因果鏈</t>
+          <t>有效例證</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>causal chain</t>
+          <t>effective examples</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12144,32 +12150,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>H5-3</t>
+          <t>H5-2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC</t>
+          <t>WRITE_HSF_ELABORATION</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>H5-3-3</t>
+          <t>H5-2-4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC_PROBLEM_SOLUTION</t>
+          <t>WRITE_HSF_ELABORATION_ILLUSTRATION</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>問題－解決</t>
+          <t>例示</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>problem-solution</t>
+          <t>illustration</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12206,32 +12212,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>H5-3</t>
+          <t>H5-2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC</t>
+          <t>WRITE_HSF_ELABORATION</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>H5-3-4</t>
+          <t>H5-2-5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC_CONDITION_RESULT</t>
+          <t>WRITE_HSF_ELABORATION_EXPLANATION</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>條件－結果</t>
+          <t>解釋</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>condition-result</t>
+          <t>explanation</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -12268,32 +12274,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>H5-3</t>
+          <t>H5-2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC</t>
+          <t>WRITE_HSF_ELABORATION</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>H5-3-5</t>
+          <t>H5-2-6</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC_REASON_RESULT</t>
+          <t>WRITE_HSF_ELABORATION_DETAIL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>理由－結果</t>
+          <t>細節</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>reason-result</t>
+          <t>detail</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -12330,32 +12336,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>H5-3</t>
+          <t>H5-2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC</t>
+          <t>WRITE_HSF_ELABORATION</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>H5-3-6</t>
+          <t>H5-2-7</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>WRITE_HSF_LOGIC_PROCESS_DEVELOPMENT</t>
+          <t>WRITE_HSF_ELABORATION_IDEA_EXPLAIN_EXTEND</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>過程推展</t>
+          <t>Idea → Explain → Extend 展開</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>process development</t>
+          <t>Idea → Explain → Extend</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -12392,32 +12398,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>H5-4</t>
+          <t>H5-3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE</t>
+          <t>WRITE_HSF_LOGIC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>H5-4-1</t>
+          <t>H5-3-1</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE_COMPARE_CONTRAST</t>
+          <t>WRITE_HSF_LOGIC_CAUSE_EFFECT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>比較對照</t>
+          <t>因果轉承</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>compare &amp; contrast</t>
+          <t>cause-effect</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -12454,32 +12460,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>H5-4</t>
+          <t>H5-3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE</t>
+          <t>WRITE_HSF_LOGIC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>H5-4-2</t>
+          <t>H5-3-2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE_CATEGORIZATION</t>
+          <t>WRITE_HSF_LOGIC_CAUSAL_CHAIN</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>因果鏈</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>categorization</t>
+          <t>causal chain</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -12516,32 +12522,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>H5-4</t>
+          <t>H5-3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE</t>
+          <t>WRITE_HSF_LOGIC</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>H5-4-3</t>
+          <t>H5-3-3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE_GROUPING</t>
+          <t>WRITE_HSF_LOGIC_PROBLEM_SOLUTION</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>歸類</t>
+          <t>問題－解決</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>grouping</t>
+          <t>problem-solution</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -12578,32 +12584,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>H5-4</t>
+          <t>H5-3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE</t>
+          <t>WRITE_HSF_LOGIC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>H5-4-4</t>
+          <t>H5-3-4</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE_MULTIPLE_PERSPECTIVES</t>
+          <t>WRITE_HSF_LOGIC_CONDITION_RESULT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>多重觀點</t>
+          <t>條件－結果</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>multiple perspectives</t>
+          <t>condition-result</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -12640,32 +12646,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>H5-4</t>
+          <t>H5-3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE</t>
+          <t>WRITE_HSF_LOGIC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>H5-4-5</t>
+          <t>H5-3-5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE_STAKEHOLDER_ANALYSIS</t>
+          <t>WRITE_HSF_LOGIC_REASON_RESULT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>關係人分析</t>
+          <t>理由－結果</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>stakeholder analysis</t>
+          <t>reason-result</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12702,32 +12708,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>H5-4</t>
+          <t>H5-3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE</t>
+          <t>WRITE_HSF_LOGIC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>H5-4-6</t>
+          <t>H5-3-6</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MULTIANGLE_DIFFERENT_DIMENSIONS</t>
+          <t>WRITE_HSF_LOGIC_PROCESS_DEVELOPMENT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>不同面向</t>
+          <t>過程推展</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>different dimensions</t>
+          <t>process development</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12764,32 +12770,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>H5-5</t>
+          <t>H5-4</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT</t>
+          <t>WRITE_HSF_MULTIANGLE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>H5-5-1</t>
+          <t>H5-4-1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT_LESSON_LEARNED</t>
+          <t>WRITE_HSF_MULTIANGLE_COMPARE_CONTRAST</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>學到的道理</t>
+          <t>比較對照</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>lesson learned</t>
+          <t>compare &amp; contrast</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12826,32 +12832,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>H5-5</t>
+          <t>H5-4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT</t>
+          <t>WRITE_HSF_MULTIANGLE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>H5-5-2</t>
+          <t>H5-4-2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT_MEANING</t>
+          <t>WRITE_HSF_MULTIANGLE_CATEGORIZATION</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>意義</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>meaning</t>
+          <t>categorization</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12888,32 +12894,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>H5-5</t>
+          <t>H5-4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT</t>
+          <t>WRITE_HSF_MULTIANGLE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>H5-5-3</t>
+          <t>H5-4-3</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT_IMPLICATION</t>
+          <t>WRITE_HSF_MULTIANGLE_GROUPING</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>意涵</t>
+          <t>歸類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>implication</t>
+          <t>grouping</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -12950,32 +12956,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>H5-5</t>
+          <t>H5-4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT</t>
+          <t>WRITE_HSF_MULTIANGLE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>H5-5-4</t>
+          <t>H5-4-4</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT_PERSPECTIVE_SHIFT</t>
+          <t>WRITE_HSF_MULTIANGLE_MULTIPLE_PERSPECTIVES</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>觀點轉變</t>
+          <t>多重觀點</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>perspective shift</t>
+          <t>multiple perspectives</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -13012,32 +13018,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>H5-5</t>
+          <t>H5-4</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT</t>
+          <t>WRITE_HSF_MULTIANGLE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>H5-5-5</t>
+          <t>H5-4-5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT_DEEPER_INTERPRETATION</t>
+          <t>WRITE_HSF_MULTIANGLE_STAKEHOLDER_ANALYSIS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>更深層詮釋</t>
+          <t>關係人分析</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>deeper interpretation</t>
+          <t>stakeholder analysis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -13074,30 +13080,34 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>H5-5</t>
+          <t>H5-4</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT</t>
+          <t>WRITE_HSF_MULTIANGLE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>H5-5-6</t>
+          <t>H5-4-6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WRITE_HSF_INSIGHT_SO_WHAT</t>
+          <t>WRITE_HSF_MULTIANGLE_DIFFERENT_DIMENSIONS</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>「so what?」</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
+          <t>不同面向</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>different dimensions</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
@@ -13132,32 +13142,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>H5-6</t>
+          <t>H5-5</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+          <t>WRITE_HSF_INSIGHT</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>H5-6-1</t>
+          <t>H5-5-1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE_SYNTHESIS</t>
+          <t>WRITE_HSF_INSIGHT_LESSON_LEARNED</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>綜合收束</t>
+          <t>學到的道理</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>lesson learned</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -13194,32 +13204,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>H5-6</t>
+          <t>H5-5</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+          <t>WRITE_HSF_INSIGHT</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>H5-6-2</t>
+          <t>H5-5-2</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE_RESOLUTION</t>
+          <t>WRITE_HSF_INSIGHT_MEANING</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>收束解決</t>
+          <t>意義</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>resolution</t>
+          <t>meaning</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -13256,22 +13266,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>H5-6</t>
+          <t>H5-5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+          <t>WRITE_HSF_INSIGHT</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>H5-6-3</t>
+          <t>H5-5-3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE_IMPLICATION</t>
+          <t>WRITE_HSF_INSIGHT_IMPLICATION</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -13318,32 +13328,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>H5-6</t>
+          <t>H5-5</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+          <t>WRITE_HSF_INSIGHT</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>H5-6-4</t>
+          <t>H5-5-4</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE_RETURN_TO_CENTRAL_IDEA</t>
+          <t>WRITE_HSF_INSIGHT_PERSPECTIVE_SHIFT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>回到核心概念</t>
+          <t>觀點轉變</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>return to central idea</t>
+          <t>perspective shift</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13380,32 +13390,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>H5-6</t>
+          <t>H5-5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+          <t>WRITE_HSF_INSIGHT</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>H5-6-5</t>
+          <t>H5-5-5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>WRITE_HSF_MEANINGFUL_CLOSE_ANSWERING_THE_TASK</t>
+          <t>WRITE_HSF_INSIGHT_DEEPER_INTERPRETATION</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>回應題目要求</t>
+          <t>更深層詮釋</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>answering the task</t>
+          <t>deeper interpretation</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13442,55 +13452,422 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
+          <t>H5-5</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_INSIGHT</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>H5-5-6</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_INSIGHT_SO_WHAT</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>「so what?」</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>H5-6</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>H5-6-1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE_SYNTHESIS</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>綜合收束</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>H5-6</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>H5-6-2</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE_RESOLUTION</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>收束解決</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>resolution</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>H5-6</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>H5-6-3</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE_IMPLICATION</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>意涵</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>implication</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>H5-6</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>H5-6-4</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE_RETURN_TO_CENTRAL_IDEA</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>回到核心概念</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>return to central idea</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>H5-6</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>H5-6-5</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE_ANSWERING_THE_TASK</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>回應題目要求</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>answering the task</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>H5-6</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>WRITE_HSF_MEANINGFUL_CLOSE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
         <is>
           <t>H5-6-6</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>WRITE_HSF_MEANINGFUL_CLOSE_FUTURE_IMPLICATION</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>未來意涵</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>future implication</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>源自 workbook High_Score_Features「Sub-skills / 判斷項目」逐項拆分（分隔符：；）。</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>OWNER_ONLY</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>OWNER_ONLY</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
